--- a/data/reports/2024-06-17/2024-06-17_duplicates.xlsx
+++ b/data/reports/2024-06-17/2024-06-17_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6164,16 +6164,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6181,16 +6193,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6214,28 +6226,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6512,9 +6512,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6525,14 +6527,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6559,7 +6563,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6568,13 +6572,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6585,9 +6587,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6606,55 +6606,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6666,32 +6652,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6717,54 +6717,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6781,33 +6767,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6973,13 +6973,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7458,55 +7458,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7518,34 +7524,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7555,10 +7555,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7587,7 +7587,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7633,7 +7633,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7651,14 +7651,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7700,45 +7700,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7756,30 +7744,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -7911,48 +7911,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -7971,25 +7957,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8140,45 +8140,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8198,24 +8186,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8247,48 +8247,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8309,14 +8303,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8324,22 +8322,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8665,9 +8665,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8711,15 +8717,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8758,55 +8758,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8818,32 +8804,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8978,7 +8978,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -8995,12 +8995,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -9024,7 +9024,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9109,38 +9109,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9155,41 +9167,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9236,7 +9236,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9342,7 +9342,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -9836,13 +9836,13 @@
         <v>27</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>407</v>
@@ -9902,7 +9902,7 @@
         <v>414</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>415</v>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R75" s="1" t="s">
         <v>30</v>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>30</v>
@@ -10046,7 +10046,7 @@
         <v>433</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>26</v>
@@ -10075,7 +10075,7 @@
         <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>28</v>
@@ -10185,7 +10185,7 @@
         <v>245</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>441</v>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>30</v>
@@ -10287,7 +10287,7 @@
         <v>30</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -10742,7 +10742,7 @@
         <v>501</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>26</v>
@@ -10782,10 +10782,10 @@
         <v>505</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>504</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R91" s="1" t="s">
         <v>30</v>
@@ -10991,7 +10991,7 @@
         <v>59</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>521</v>
@@ -11033,7 +11033,7 @@
         <v>30</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -11042,21 +11042,21 @@
         <v>527</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>528</v>
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>529</v>
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>30</v>
@@ -11195,7 +11195,7 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -11213,14 +11213,14 @@
         <v>543</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>544</v>
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>30</v>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>30</v>
@@ -11362,13 +11362,13 @@
         <v>27</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>560</v>
@@ -11377,7 +11377,7 @@
         <v>59</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>559</v>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>30</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>26</v>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R106" s="1" t="s">
         <v>30</v>
@@ -11771,7 +11771,7 @@
         <v>608</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>605</v>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>30</v>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R113" s="1" t="s">
         <v>30</v>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>30</v>
@@ -12251,7 +12251,7 @@
         <v>659</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>655</v>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>30</v>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>30</v>
@@ -12969,7 +12969,7 @@
         <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R134" s="1" t="s">
         <v>30</v>
@@ -13233,7 +13233,7 @@
         <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>28</v>
@@ -13257,7 +13257,7 @@
         <v>762</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O136" s="1" t="s">
         <v>765</v>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>30</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R139" s="1" t="s">
         <v>30</v>
@@ -13547,7 +13547,7 @@
         <v>798</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>796</v>
@@ -13605,7 +13605,7 @@
         <v>245</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>802</v>
@@ -13661,7 +13661,7 @@
         <v>629</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>808</v>
@@ -13834,13 +13834,13 @@
         <v>27</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>830</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J146" s="1" t="s">
         <v>831</v>
@@ -13849,7 +13849,7 @@
         <v>832</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M146" s="1" t="s">
         <v>829</v>
@@ -13913,7 +13913,7 @@
         <v>841</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>842</v>
@@ -13957,7 +13957,7 @@
         <v>30</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>847</v>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>30</v>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>30</v>
@@ -14187,7 +14187,7 @@
         <v>293</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M152" s="1" t="s">
         <v>874</v>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>30</v>
@@ -14479,7 +14479,7 @@
         <v>899</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="1" t="s">
@@ -14532,7 +14532,7 @@
         <v>905</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>906</v>
@@ -14606,7 +14606,7 @@
         <v>915</v>
       </c>
       <c r="Q160" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R160" s="1" t="s">
         <v>26</v>
@@ -14682,7 +14682,7 @@
         <v>27</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H162" s="1"/>
       <c r="I162" s="1"/>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>26</v>
@@ -14781,7 +14781,7 @@
         <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>28</v>
@@ -14805,14 +14805,14 @@
         <v>934</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O164" s="1" t="s">
         <v>935</v>
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>30</v>
@@ -14846,7 +14846,7 @@
         <v>27</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>939</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="P165" s="1"/>
       <c r="Q165" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>30</v>
@@ -14905,7 +14905,7 @@
         <v>30</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -14917,11 +14917,11 @@
         <v>59</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M166" s="1"/>
       <c r="N166" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O166" s="1" t="s">
         <v>947</v>
@@ -15109,7 +15109,7 @@
         <v>30</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -15118,21 +15118,21 @@
         <v>964</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L170" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>965</v>
       </c>
       <c r="P170" s="1"/>
       <c r="Q170" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>30</v>
@@ -15217,7 +15217,7 @@
         <v>59</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M172" s="1"/>
       <c r="N172" s="1" t="s">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>30</v>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>26</v>
@@ -15344,7 +15344,7 @@
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>30</v>
@@ -15406,7 +15406,7 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>30</v>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>30</v>
@@ -15793,7 +15793,7 @@
         <v>165</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M182" s="1" t="s">
         <v>1043</v>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>30</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="P184" s="1"/>
       <c r="Q184" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>26</v>
@@ -15980,7 +15980,7 @@
       </c>
       <c r="P185" s="1"/>
       <c r="Q185" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>26</v>
@@ -16027,7 +16027,7 @@
         <v>1071</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M186" s="1" t="s">
         <v>1072</v>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>30</v>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>30</v>
@@ -16372,13 +16372,13 @@
         <v>27</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>1109</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
@@ -16415,7 +16415,7 @@
         <v>30</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G193" s="1"/>
       <c r="H193" s="1"/>
@@ -16433,14 +16433,14 @@
         <v>1114</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O193" s="1" t="s">
         <v>1115</v>
       </c>
       <c r="P193" s="1"/>
       <c r="Q193" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>30</v>
@@ -16474,13 +16474,13 @@
         <v>27</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>1119</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J194" s="1"/>
       <c r="K194" s="1"/>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R196" s="1" t="s">
         <v>26</v>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="P200" s="1"/>
       <c r="Q200" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R200" s="1" t="s">
         <v>30</v>
@@ -16875,7 +16875,7 @@
         <v>1160</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M201" s="1"/>
       <c r="N201" s="1" t="s">
@@ -17027,7 +17027,7 @@
         <v>30</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G204" s="1"/>
       <c r="H204" s="1"/>
@@ -17039,18 +17039,18 @@
         <v>450</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M204" s="1"/>
       <c r="N204" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O204" s="1" t="s">
         <v>1173</v>
       </c>
       <c r="P204" s="1"/>
       <c r="Q204" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>30</v>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P205" s="1"/>
       <c r="Q205" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>30</v>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>30</v>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>30</v>
@@ -17274,7 +17274,7 @@
         <v>1200</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L208" s="1" t="s">
         <v>1201</v>
@@ -17333,7 +17333,7 @@
         <v>59</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M209" s="1" t="s">
         <v>1209</v>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>30</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17470,7 +17470,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17503,7 +17503,7 @@
         <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>1235</v>
@@ -17523,7 +17523,7 @@
         <v>1234</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>1238</v>
@@ -17565,16 +17565,16 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1236</v>
@@ -17589,7 +17589,7 @@
         <v>1234</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1238</v>
@@ -17644,10 +17644,10 @@
         <v>1247</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M214" s="1" t="s">
         <v>1248</v>
@@ -17778,7 +17778,7 @@
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R216" s="1" t="s">
         <v>30</v>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -17926,7 +17926,7 @@
         <v>1198</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
@@ -17950,7 +17950,7 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R219" s="1" t="s">
         <v>30</v>
@@ -18001,7 +18001,7 @@
         <v>1280</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M220" s="1" t="s">
         <v>1281</v>
@@ -18061,7 +18061,7 @@
         <v>1288</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1289</v>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="P221" s="1"/>
       <c r="Q221" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R221" s="1" t="s">
         <v>30</v>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="P222" s="1"/>
       <c r="Q222" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R222" s="1" t="s">
         <v>26</v>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>26</v>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>30</v>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>30</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>30</v>
@@ -18502,7 +18502,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18538,13 +18538,13 @@
         <v>27</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>1343</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>1344</v>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>30</v>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>30</v>
@@ -18677,7 +18677,7 @@
         <v>165</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>1361</v>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>30</v>
@@ -18809,7 +18809,7 @@
         <v>629</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>1377</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18888,7 +18888,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -18936,7 +18936,7 @@
         <v>1393</v>
       </c>
       <c r="K235" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L235" s="1" t="s">
         <v>1394</v>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>30</v>
@@ -19016,7 +19016,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>30</v>
@@ -19196,7 +19196,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>30</v>
@@ -19311,7 +19311,7 @@
         <v>1430</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M241" s="1" t="s">
         <v>1435</v>
@@ -19384,7 +19384,7 @@
       </c>
       <c r="P242" s="1"/>
       <c r="Q242" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R242" s="1" t="s">
         <v>26</v>
@@ -19428,10 +19428,10 @@
         <v>1446</v>
       </c>
       <c r="K243" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M243" s="1" t="s">
         <v>1445</v>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R243" s="1" t="s">
         <v>30</v>
@@ -19540,13 +19540,13 @@
         <v>27</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>1452</v>
@@ -19630,7 +19630,7 @@
         <v>1466</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R246" s="1" t="s">
         <v>30</v>
@@ -19743,7 +19743,7 @@
         <v>293</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1479</v>
@@ -19756,7 +19756,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>30</v>
@@ -19805,7 +19805,7 @@
         <v>293</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1479</v>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>30</v>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>30</v>
@@ -20349,7 +20349,7 @@
         <v>1546</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>1542</v>
@@ -20362,7 +20362,7 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R258" s="1" t="s">
         <v>30</v>
@@ -20411,7 +20411,7 @@
         <v>1546</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>1552</v>
@@ -20424,7 +20424,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>30</v>
@@ -20535,7 +20535,7 @@
         <v>568</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M261" s="1" t="s">
         <v>1567</v>
@@ -20548,7 +20548,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>30</v>
@@ -20584,13 +20584,13 @@
         <v>27</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>1573</v>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R262" s="1" t="s">
         <v>30</v>
@@ -20659,7 +20659,7 @@
         <v>293</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>1581</v>
@@ -20723,7 +20723,7 @@
         <v>1590</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>1591</v>
@@ -20736,7 +20736,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>30</v>
@@ -20847,7 +20847,7 @@
         <v>629</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1603</v>
@@ -20909,7 +20909,7 @@
         <v>629</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1603</v>
@@ -20973,7 +20973,7 @@
         <v>59</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1615</v>
@@ -21037,7 +21037,7 @@
         <v>59</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1624</v>
@@ -21086,13 +21086,13 @@
         <v>209</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>1631</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>1632</v>
@@ -21116,7 +21116,7 @@
         <v>1635</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>30</v>
@@ -21152,13 +21152,13 @@
         <v>209</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>1631</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>1632</v>
@@ -21182,7 +21182,7 @@
         <v>1635</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>30</v>
@@ -21246,7 +21246,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>30</v>
@@ -21308,7 +21308,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>30</v>
@@ -21368,7 +21368,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>30</v>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>30</v>
@@ -21552,7 +21552,7 @@
       </c>
       <c r="P277" s="1"/>
       <c r="Q277" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>30</v>
@@ -21614,7 +21614,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P282" s="1"/>
       <c r="Q282" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R282" s="1" t="s">
         <v>30</v>
@@ -21916,7 +21916,7 @@
         <v>1726</v>
       </c>
       <c r="Q283" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
         <v>30</v>
@@ -21951,7 +21951,7 @@
         <v>30</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>1731</v>
@@ -21965,20 +21965,20 @@
         <v>1733</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M284" s="1" t="s">
         <v>1730</v>
       </c>
       <c r="N284" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O284" s="1" t="s">
         <v>1734</v>
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R284" s="1" t="s">
         <v>30</v>
@@ -22011,7 +22011,7 @@
         <v>30</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G285" s="1"/>
       <c r="H285" s="1"/>
@@ -22023,20 +22023,20 @@
         <v>1738</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M285" s="1" t="s">
         <v>1730</v>
       </c>
       <c r="N285" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O285" s="1" t="s">
         <v>1739</v>
       </c>
       <c r="P285" s="1"/>
       <c r="Q285" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R285" s="1" t="s">
         <v>30</v>
